--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428420</v>
+        <v>125428356</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577815</v>
+        <v>577823</v>
       </c>
       <c r="R2" t="n">
-        <v>7084302</v>
+        <v>7084307</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -1095,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428356</v>
+        <v>125428420</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,38 +1103,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577823</v>
+        <v>577815</v>
       </c>
       <c r="R6" t="n">
-        <v>7084307</v>
+        <v>7084302</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428356</v>
+        <v>125428405</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>78683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577823</v>
+        <v>577821</v>
       </c>
       <c r="R2" t="n">
-        <v>7084307</v>
+        <v>7084314</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428421</v>
+        <v>125428406</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577819</v>
+        <v>577828</v>
       </c>
       <c r="R3" t="n">
-        <v>7084332</v>
+        <v>7084271</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428406</v>
+        <v>125428420</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577828</v>
+        <v>577815</v>
       </c>
       <c r="R4" t="n">
-        <v>7084271</v>
+        <v>7084302</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428405</v>
+        <v>125428356</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>79565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577821</v>
+        <v>577823</v>
       </c>
       <c r="R5" t="n">
-        <v>7084314</v>
+        <v>7084307</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428420</v>
+        <v>125428421</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577815</v>
+        <v>577819</v>
       </c>
       <c r="R6" t="n">
-        <v>7084302</v>
+        <v>7084332</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428406</v>
+        <v>125428420</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577828</v>
+        <v>577815</v>
       </c>
       <c r="R3" t="n">
-        <v>7084271</v>
+        <v>7084302</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428420</v>
+        <v>125428421</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -918,7 +918,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577815</v>
+        <v>577819</v>
       </c>
       <c r="R4" t="n">
-        <v>7084302</v>
+        <v>7084332</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428421</v>
+        <v>125428406</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577819</v>
+        <v>577828</v>
       </c>
       <c r="R6" t="n">
-        <v>7084332</v>
+        <v>7084271</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428356</v>
+        <v>125428421</v>
       </c>
       <c r="B2" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577823</v>
+        <v>577819</v>
       </c>
       <c r="R2" t="n">
-        <v>7084307</v>
+        <v>7084332</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428421</v>
+        <v>125428356</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>79585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577819</v>
+        <v>577823</v>
       </c>
       <c r="R3" t="n">
-        <v>7084332</v>
+        <v>7084307</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -876,7 +876,7 @@
         <v>125428406</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125428420</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428421</v>
+        <v>125428356</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>79585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577819</v>
+        <v>577823</v>
       </c>
       <c r="R2" t="n">
-        <v>7084332</v>
+        <v>7084307</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -776,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428356</v>
+        <v>125428421</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577823</v>
+        <v>577819</v>
       </c>
       <c r="R3" t="n">
-        <v>7084307</v>
+        <v>7084332</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125428356</v>
       </c>
       <c r="B2" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125428421</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>125428406</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125428420</v>
       </c>
       <c r="B5" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>125428405</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428356</v>
+        <v>125428421</v>
       </c>
       <c r="B2" t="n">
-        <v>79586</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577823</v>
+        <v>577819</v>
       </c>
       <c r="R2" t="n">
-        <v>7084307</v>
+        <v>7084332</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428421</v>
+        <v>125428356</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>79590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577819</v>
+        <v>577823</v>
       </c>
       <c r="R3" t="n">
-        <v>7084332</v>
+        <v>7084307</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -876,7 +876,7 @@
         <v>125428406</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125428420</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>125428405</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428421</v>
+        <v>125428356</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>79590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577819</v>
+        <v>577823</v>
       </c>
       <c r="R2" t="n">
-        <v>7084332</v>
+        <v>7084307</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -776,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428356</v>
+        <v>125428421</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577823</v>
+        <v>577819</v>
       </c>
       <c r="R3" t="n">
-        <v>7084307</v>
+        <v>7084332</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -876,7 +876,7 @@
         <v>125428406</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125428420</v>
       </c>
       <c r="B5" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428356</v>
+        <v>125428365</v>
       </c>
       <c r="B2" t="n">
-        <v>79590</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,22 +710,22 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577823</v>
+        <v>577840</v>
       </c>
       <c r="R2" t="n">
-        <v>7084307</v>
+        <v>7084230</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västernorrland</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Fjällsjö</t>
+          <t>Junsele</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428421</v>
+        <v>125428405</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577819</v>
+        <v>577821</v>
       </c>
       <c r="R3" t="n">
-        <v>7084332</v>
+        <v>7084314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,61 +869,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428406</v>
+        <v>125428355</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577828</v>
+        <v>577852</v>
       </c>
       <c r="R4" t="n">
-        <v>7084271</v>
+        <v>7084241</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västernorrland</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -937,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Fjällsjö</t>
+          <t>Junsele</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -974,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428420</v>
+        <v>125428356</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577815</v>
+        <v>577823</v>
       </c>
       <c r="R5" t="n">
-        <v>7084302</v>
+        <v>7084307</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1075,45 +1063,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428405</v>
+        <v>125428406</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577821</v>
+        <v>577828</v>
       </c>
       <c r="R6" t="n">
-        <v>7084314</v>
+        <v>7084271</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,6 +1161,208 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125428420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skirsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577815</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7084302</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125428421</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skirsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577819</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7084332</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23632-2025 artfynd.xlsx
+++ b/artfynd/A 23632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428356</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428420</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,8 +1398,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125428421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>